--- a/CUSTOMER_LIST.xlsx
+++ b/CUSTOMER_LIST.xlsx
@@ -1,27 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_AEB0C6D37D35B7D734F3E36E5AAAF699363F7EE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone.sharepoint.com/sites/POpriority/Shared Documents/Project Eagles/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{35E028A0-FDFF-4DB6-91CF-EA3AB041B4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5358A00-B467-4642-8776-6479FF1FE9D3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{3CEF025D-F35F-4926-BAF1-D319640BE415}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029" concurrentManualCount="12"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+  <si>
+    <t>OUTPUT</t>
+  </si>
+  <si>
+    <t>AGRI</t>
+  </si>
+  <si>
+    <t>CLUB</t>
+  </si>
+  <si>
+    <t>DBD</t>
+  </si>
+  <si>
+    <t>ECOMMERCE</t>
+  </si>
+  <si>
+    <t>HYPER</t>
+  </si>
+  <si>
+    <t>NATIONAL</t>
+  </si>
+  <si>
+    <t>PX</t>
+  </si>
+  <si>
+    <t>BASE DBD</t>
+  </si>
+  <si>
+    <t>COSTCO</t>
+  </si>
+  <si>
+    <t>COUPANG</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>EMART</t>
+  </si>
+  <si>
+    <t>HOMEPLUS</t>
+  </si>
+  <si>
+    <t>NAVER</t>
+  </si>
+  <si>
+    <t>PGLAND</t>
+  </si>
+  <si>
+    <t>TRADERS</t>
+  </si>
+  <si>
+    <t>COSTCO, TRADERS</t>
+  </si>
+  <si>
+    <t>OLIVEYOUNG</t>
+  </si>
+  <si>
+    <t>CVS</t>
+  </si>
+  <si>
+    <t>EMART, HOMEPLUS, LOTTEMART</t>
+  </si>
+  <si>
+    <t>LOTTEMART</t>
+  </si>
+  <si>
+    <t>COUPANG, NAVER, PGLAND, KURLY</t>
+  </si>
+  <si>
+    <t>KURLY</t>
+  </si>
+  <si>
+    <t>SPECIFIC CUSTOMER CODE</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>DBD-DaeguPG</t>
+  </si>
+  <si>
+    <t>DBD-HONAM</t>
+  </si>
+  <si>
+    <t>DBD-JANGWON</t>
+  </si>
+  <si>
+    <t>DBD-MiraeJonghapMulryu</t>
+  </si>
+  <si>
+    <t>DBD-PGP</t>
+  </si>
+  <si>
+    <t>BASE DBD, MQ, DaeguPG, HONAM, JANGWON, MIRAEJONGHAPMULRYU, PGP</t>
+  </si>
+  <si>
+    <t>DaeguPG</t>
+  </si>
+  <si>
+    <t>HONAM</t>
+  </si>
+  <si>
+    <t>JANGWON</t>
+  </si>
+  <si>
+    <t>PGP</t>
+  </si>
+  <si>
+    <t>DBD-MQ</t>
+  </si>
+  <si>
+    <t>MQ</t>
+  </si>
+  <si>
+    <t>MIRAEJONGHAPMULRYU</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,7 +195,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -86,13 +224,13 @@
         <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="145F82"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E87331"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="186C24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
         <a:srgbClr val="0F9ED5"/>
@@ -112,7 +250,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -378,18 +516,312 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F9526A7-DC75-43BB-8E7B-C2C86D471917}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="67.7109375" customWidth="1"/>
+    <col min="3" max="3" width="79.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2001549758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>2003202644</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>2001640272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>2002861931</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>2002910779</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>2002871409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>2003181036</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>2002424920</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>2001592222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>2000380365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>2002966999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>2003284351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>2001669469</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>2002486894</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>2003142554</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>2003223809</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>2003226967</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>2003212785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25">
+        <v>2000554450</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26">
+        <v>2002936322</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>2002684481</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Business Use&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+  <customProperties>
+    <customPr name="_pios_id" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
@@ -637,13 +1069,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{258B45A3-E2D5-44D7-A7B9-8E265F541C26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10D900A7-9DAE-4C99-9082-1C7C287F68A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6C12465-D2C2-4B56-B29D-F77C3444F5A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{320841E3-3EA4-49DA-A9FA-EFB1154E06D9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
+    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0956D958-DD07-4CD0-9DEB-149C01DD8011}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1644D4D0-FA03-43A5-B796-77A60CBD42E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
+    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CUSTOMER_LIST.xlsx
+++ b/CUSTOMER_LIST.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="83" documentId="8_{35E028A0-FDFF-4DB6-91CF-EA3AB041B4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5358A00-B467-4642-8776-6479FF1FE9D3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{3CEF025D-F35F-4926-BAF1-D319640BE415}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3CEF025D-F35F-4926-BAF1-D319640BE415}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentManualCount="12"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -826,17 +826,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6c0e7a184c0233f586ea7baba2e967b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6204f9fca8cd82ddbd42930875406446" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bed13c56006c51b90ac333a6ae976798">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eefb45b713b0d33d9a84026b36f62d67" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -857,6 +848,7 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -914,6 +906,11 @@
     <xsd:element name="MediaServiceEventHashCode" ma:index="20" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1057,6 +1054,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1069,28 +1075,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D7C7D8-7F40-4FDF-BFB0-49BA95EFB460}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10D900A7-9DAE-4C99-9082-1C7C287F68A5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{320841E3-3EA4-49DA-A9FA-EFB1154E06D9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
-    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CUSTOMER_LIST.xlsx
+++ b/CUSTOMER_LIST.xlsx
@@ -826,8 +826,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bed13c56006c51b90ac333a6ae976798">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eefb45b713b0d33d9a84026b36f62d67" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9416936a3b57ab26e55784844af5429">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9218ed845bf90baf0025c167a9057e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -849,6 +849,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:i0f84bba906045b4af568ee102a52dcb" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -952,6 +953,13 @@
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="i0f84bba906045b4af568ee102a52dcb" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="i0f84bba906045b4af568ee102a52dcb" ma:taxonomyFieldName="RevIMBCS" ma:displayName="Retention Policy" ma:indexed="true" ma:default="5;#Daily Work Documents [Standard]|c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b" ma:fieldId="{20f84bba-9060-45b4-af56-8ee102a52dcb}" ma:sspId="c81b625c-6132-4315-8b99-2d7d4df07560" ma:termSetId="1d8deb5c-7ccc-4e04-a1de-f52ad8333138" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
@@ -1069,13 +1077,23 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="57147975-5687-4135-8263-39f5df548c17">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74" xsi:nil="true"/>
+    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Value>5</Value>
+    </TaxCatchAll>
+    <i0f84bba906045b4af568ee102a52dcb xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Daily Work Documents [Standard]</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b</TermId>
+        </TermInfo>
+      </Terms>
+    </i0f84bba906045b4af568ee102a52dcb>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D7C7D8-7F40-4FDF-BFB0-49BA95EFB460}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C5ED66-C132-464A-A20C-7B13F019C20A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
